--- a/Excel/PillConfig2.xlsx
+++ b/Excel/PillConfig2.xlsx
@@ -1248,7 +1248,7 @@
         <v>8</v>
       </c>
       <c r="G6" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H6" s="1">
         <v>10</v>
@@ -1271,7 +1271,7 @@
         <v>7</v>
       </c>
       <c r="G7" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H7" s="1">
         <v>10</v>
@@ -1294,7 +1294,7 @@
         <v>12</v>
       </c>
       <c r="G8" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H8" s="1">
         <v>10</v>
@@ -1317,7 +1317,7 @@
         <v>13</v>
       </c>
       <c r="G9" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H9" s="1">
         <v>10</v>
@@ -1340,7 +1340,7 @@
         <v>9</v>
       </c>
       <c r="G10" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H10" s="1">
         <v>10</v>
@@ -1363,7 +1363,7 @@
         <v>10</v>
       </c>
       <c r="G11" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H11" s="1">
         <v>10</v>
@@ -1386,7 +1386,7 @@
         <v>33</v>
       </c>
       <c r="G12" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H12" s="1">
         <v>10</v>
@@ -1409,7 +1409,7 @@
         <v>34</v>
       </c>
       <c r="G13" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H13" s="1">
         <v>10</v>
@@ -1432,7 +1432,7 @@
         <v>35</v>
       </c>
       <c r="G14" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H14" s="1">
         <v>10</v>
@@ -1456,7 +1456,7 @@
         <v>2003</v>
       </c>
       <c r="G16" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H16" s="1">
         <v>30</v>
@@ -1480,7 +1480,7 @@
         <v>2002</v>
       </c>
       <c r="G17" s="1">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H17" s="1">
         <v>30</v>
@@ -1505,7 +1505,7 @@
         <v>2012</v>
       </c>
       <c r="G18" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H18" s="1">
         <v>30</v>
@@ -1529,7 +1529,7 @@
         <v>2007</v>
       </c>
       <c r="G19" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H19" s="1">
         <v>30</v>
@@ -1553,7 +1553,7 @@
         <v>2008</v>
       </c>
       <c r="G20" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H20" s="1">
         <v>30</v>
@@ -1581,7 +1581,7 @@
         <v>2009</v>
       </c>
       <c r="G21" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H21" s="1">
         <v>30</v>
@@ -1609,7 +1609,7 @@
         <v>2003</v>
       </c>
       <c r="G22" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H22" s="1">
         <v>30</v>
@@ -1637,7 +1637,7 @@
         <v>2002</v>
       </c>
       <c r="G23" s="1">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H23" s="1">
         <v>30</v>
@@ -1665,7 +1665,7 @@
         <v>2012</v>
       </c>
       <c r="G24" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H24" s="1">
         <v>30</v>
@@ -1693,7 +1693,7 @@
         <v>32</v>
       </c>
       <c r="G25" s="1">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="H25" s="1">
         <v>30</v>
@@ -1721,7 +1721,7 @@
         <v>31</v>
       </c>
       <c r="G26" s="1">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="H26" s="1">
         <v>30</v>
@@ -1749,7 +1749,7 @@
         <v>2003</v>
       </c>
       <c r="G27" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H27" s="1">
         <v>30</v>
@@ -1777,7 +1777,7 @@
         <v>2002</v>
       </c>
       <c r="G28" s="1">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H28" s="1">
         <v>30</v>
@@ -1805,7 +1805,7 @@
         <v>2012</v>
       </c>
       <c r="G29" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H29" s="1">
         <v>30</v>
@@ -1829,7 +1829,7 @@
         <v>2005</v>
       </c>
       <c r="G30" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H30" s="1">
         <v>30</v>
@@ -1853,7 +1853,7 @@
         <v>2006</v>
       </c>
       <c r="G31" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H31" s="1">
         <v>30</v>
@@ -1877,7 +1877,7 @@
         <v>2010</v>
       </c>
       <c r="G32" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H32" s="1">
         <v>30</v>
@@ -1901,7 +1901,7 @@
         <v>2003</v>
       </c>
       <c r="G33" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H33" s="1">
         <v>30</v>
@@ -1925,7 +1925,7 @@
         <v>2002</v>
       </c>
       <c r="G34" s="1">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H34" s="1">
         <v>30</v>
@@ -1949,7 +1949,7 @@
         <v>2012</v>
       </c>
       <c r="G35" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H35" s="1">
         <v>30</v>

--- a/Excel/PillConfig2.xlsx
+++ b/Excel/PillConfig2.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="32">
   <si>
     <t>ID</t>
   </si>
@@ -129,6 +129,15 @@
     <t>韧性倍率</t>
   </si>
   <si>
+    <t>攻击倍率</t>
+  </si>
+  <si>
+    <t>命中</t>
+  </si>
+  <si>
+    <t>闪避</t>
+  </si>
+  <si>
     <t>物伤倍率</t>
   </si>
   <si>
@@ -138,10 +147,7 @@
     <t>道伤倍率</t>
   </si>
   <si>
-    <t>命中</t>
-  </si>
-  <si>
-    <t>闪避</t>
+    <t>物攻倍率</t>
   </si>
   <si>
     <t>魔攻倍率</t>
@@ -1271,7 +1277,7 @@
         <v>7</v>
       </c>
       <c r="G7" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H7" s="1">
         <v>10</v>
@@ -1340,7 +1346,7 @@
         <v>9</v>
       </c>
       <c r="G10" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H10" s="1">
         <v>10</v>
@@ -1456,7 +1462,7 @@
         <v>2003</v>
       </c>
       <c r="G16" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H16" s="1">
         <v>30</v>
@@ -1480,7 +1486,7 @@
         <v>2002</v>
       </c>
       <c r="G17" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H17" s="1">
         <v>30</v>
@@ -1505,7 +1511,7 @@
         <v>2012</v>
       </c>
       <c r="G18" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H18" s="1">
         <v>30</v>
@@ -1526,10 +1532,10 @@
         <v>300</v>
       </c>
       <c r="F19" s="2">
-        <v>2007</v>
+        <v>2001</v>
       </c>
       <c r="G19" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H19" s="1">
         <v>30</v>
@@ -1538,7 +1544,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="20" customHeight="1" spans="3:13">
+    <row r="20" customHeight="1" spans="3:9">
       <c r="C20" s="1">
         <v>14</v>
       </c>
@@ -1549,11 +1555,11 @@
         <f t="shared" si="0"/>
         <v>400</v>
       </c>
-      <c r="F20" s="2">
-        <v>2008</v>
+      <c r="F20" s="1">
+        <v>32</v>
       </c>
       <c r="G20" s="1">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="H20" s="1">
         <v>30</v>
@@ -1561,10 +1567,6 @@
       <c r="I20" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="J20" s="2"/>
-      <c r="K20" s="1"/>
-      <c r="L20" s="1"/>
-      <c r="M20" s="1"/>
     </row>
     <row r="21" customHeight="1" spans="3:13">
       <c r="C21" s="1">
@@ -1577,11 +1579,11 @@
         <f t="shared" si="0"/>
         <v>500</v>
       </c>
-      <c r="F21" s="2">
-        <v>2009</v>
+      <c r="F21" s="1">
+        <v>31</v>
       </c>
       <c r="G21" s="1">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="H21" s="1">
         <v>30</v>
@@ -1609,7 +1611,7 @@
         <v>2003</v>
       </c>
       <c r="G22" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H22" s="1">
         <v>30</v>
@@ -1637,7 +1639,7 @@
         <v>2002</v>
       </c>
       <c r="G23" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H23" s="1">
         <v>30</v>
@@ -1665,7 +1667,7 @@
         <v>2012</v>
       </c>
       <c r="G24" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H24" s="1">
         <v>30</v>
@@ -1689,11 +1691,11 @@
         <f t="shared" si="0"/>
         <v>900</v>
       </c>
-      <c r="F25" s="1">
-        <v>32</v>
+      <c r="F25" s="2">
+        <v>2007</v>
       </c>
       <c r="G25" s="1">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="H25" s="1">
         <v>30</v>
@@ -1717,11 +1719,11 @@
         <f t="shared" si="0"/>
         <v>1000</v>
       </c>
-      <c r="F26" s="1">
-        <v>31</v>
+      <c r="F26" s="2">
+        <v>2008</v>
       </c>
       <c r="G26" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H26" s="1">
         <v>30</v>
@@ -1745,17 +1747,17 @@
         <f t="shared" si="0"/>
         <v>1100</v>
       </c>
-      <c r="F27" s="1">
-        <v>2003</v>
+      <c r="F27" s="2">
+        <v>2009</v>
       </c>
       <c r="G27" s="1">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H27" s="1">
         <v>30</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J27" s="2"/>
       <c r="K27" s="1"/>
@@ -1773,17 +1775,17 @@
         <f t="shared" si="0"/>
         <v>1200</v>
       </c>
-      <c r="F28" s="2">
-        <v>2002</v>
+      <c r="F28" s="1">
+        <v>2003</v>
       </c>
       <c r="G28" s="1">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H28" s="1">
         <v>30</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J28" s="2"/>
       <c r="K28" s="1"/>
@@ -1802,16 +1804,16 @@
         <v>1300</v>
       </c>
       <c r="F29" s="2">
-        <v>2012</v>
+        <v>2002</v>
       </c>
       <c r="G29" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H29" s="1">
         <v>30</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="3:9">
@@ -1826,16 +1828,16 @@
         <v>1400</v>
       </c>
       <c r="F30" s="2">
-        <v>2005</v>
+        <v>2012</v>
       </c>
       <c r="G30" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H30" s="1">
         <v>30</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:9">
@@ -1850,10 +1852,10 @@
         <v>1500</v>
       </c>
       <c r="F31" s="2">
-        <v>2006</v>
+        <v>2004</v>
       </c>
       <c r="G31" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H31" s="1">
         <v>30</v>
@@ -1874,10 +1876,10 @@
         <v>1600</v>
       </c>
       <c r="F32" s="2">
-        <v>2010</v>
+        <v>2005</v>
       </c>
       <c r="G32" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H32" s="1">
         <v>30</v>
@@ -1897,17 +1899,17 @@
         <f t="shared" si="0"/>
         <v>1700</v>
       </c>
-      <c r="F33" s="1">
-        <v>2003</v>
+      <c r="F33" s="2">
+        <v>2006</v>
       </c>
       <c r="G33" s="1">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H33" s="1">
         <v>30</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:9">
@@ -1922,16 +1924,16 @@
         <v>1800</v>
       </c>
       <c r="F34" s="2">
-        <v>2002</v>
+        <v>2010</v>
       </c>
       <c r="G34" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H34" s="1">
         <v>30</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:9">
@@ -1945,17 +1947,17 @@
         <f t="shared" si="0"/>
         <v>1900</v>
       </c>
-      <c r="F35" s="2">
-        <v>2012</v>
+      <c r="F35" s="1">
+        <v>2003</v>
       </c>
       <c r="G35" s="1">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H35" s="1">
         <v>30</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/PillConfig2.xlsx
+++ b/Excel/PillConfig2.xlsx
@@ -1559,7 +1559,7 @@
         <v>32</v>
       </c>
       <c r="G20" s="1">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="H20" s="1">
         <v>30</v>
@@ -1583,7 +1583,7 @@
         <v>31</v>
       </c>
       <c r="G21" s="1">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="H21" s="1">
         <v>30</v>
